--- a/data/trending_integrated_20261020_10.xlsx
+++ b/data/trending_integrated_20261020_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10900</v>
+        <v>10870</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.52%</t>
+          <t>'+19.19%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.86</v>
       </c>
       <c r="E2" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="F2" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G2" t="n">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="H2" t="n">
         <v>0.88</v>
@@ -610,7 +610,7 @@
         <v>1.74</v>
       </c>
       <c r="O2" t="n">
-        <v>142028207560</v>
+        <v>147581263145</v>
       </c>
       <c r="P2" t="n">
         <v>11250</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>로봇, ESS, 이차전지 사업 관련 긍정적 전망. 7천억 수주잔고 및 1조 클럽 가능성 언급. 신고가 달성.</t>
+          <t>ESS, 로봇, 이차전지 사업 연관성 및 7천억 규모 수주잔고 기반 1조 시총 달성 기대. 신고가 경신 및 강한 상승세.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇', '수주잔고', '신고가']</t>
+          <t>['로봇주', '수주잔고', 'ESS']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20450</v>
+        <v>20150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+3.75%</t>
+          <t>'+2.23%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F3" t="n">
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H3" t="n">
         <v>3.07</v>
@@ -702,7 +702,7 @@
         <v>3.32</v>
       </c>
       <c r="O3" t="n">
-        <v>71414121165</v>
+        <v>73220190515</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇 사업 성장과 연계된 보안주로서의 라온시큐어 주목. 외국인 매수세 및 2만원 안착 여부 관심.</t>
+          <t>로봇 산업 성장과 함께 보안주로서의 중요성 부각. 단기 변동성 속 2만원 안착 여부 주목.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안주', '로봇', '외국인']</t>
+          <t>['보안주', '로봇', '외국인 매수']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42050</v>
+        <v>212000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-2.10%</t>
+          <t>'-2.75%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>97</v>
+        <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>69</v>
+        <v>481</v>
       </c>
       <c r="G4" t="n">
-        <v>459</v>
+        <v>1188</v>
       </c>
       <c r="H4" t="n">
-        <v>13.11</v>
+        <v>46.04</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>42950</v>
+        <v>218000</v>
       </c>
       <c r="K4" t="n">
-        <v>42600</v>
+        <v>219500</v>
       </c>
       <c r="L4" t="n">
-        <v>43200</v>
+        <v>219500</v>
       </c>
       <c r="M4" t="n">
-        <v>41750</v>
+        <v>211500</v>
       </c>
       <c r="N4" t="n">
-        <v>13.04</v>
+        <v>45.99</v>
       </c>
       <c r="O4" t="n">
-        <v>6272302675</v>
+        <v>917064036250</v>
       </c>
       <c r="P4" t="n">
-        <v>69200</v>
+        <v>374500</v>
       </c>
       <c r="Q4" t="n">
-        <v>24150</v>
+        <v>94500</v>
       </c>
       <c r="R4" t="n">
-        <v>-11000</v>
+        <v>400000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-408000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>담관암 FDA 승인 기대감과 주가 미반영에 대한 의문. Class 1 발표 및 신뢰 회복 촉구.</t>
+          <t>정부 정책 및 이재명 관련 부정적 언급과 함께 주가 하락세에 대한 우려. 반도체 산업 전망 불확실성.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['FDA승인', 'Class1', '신뢰']</t>
+          <t>['주가 관리', '반도체', '이재명 리스크']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>213000</v>
+        <v>41750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-2.29%</t>
+          <t>'-2.79%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>101</v>
       </c>
       <c r="F5" t="n">
-        <v>471</v>
+        <v>71</v>
       </c>
       <c r="G5" t="n">
-        <v>1247</v>
+        <v>481</v>
       </c>
       <c r="H5" t="n">
-        <v>46.04</v>
+        <v>13.11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>218000</v>
+        <v>42950</v>
       </c>
       <c r="K5" t="n">
-        <v>219500</v>
+        <v>42600</v>
       </c>
       <c r="L5" t="n">
-        <v>219500</v>
+        <v>43200</v>
       </c>
       <c r="M5" t="n">
-        <v>211500</v>
+        <v>41750</v>
       </c>
       <c r="N5" t="n">
-        <v>45.99</v>
+        <v>13.04</v>
       </c>
       <c r="O5" t="n">
-        <v>843327309000</v>
+        <v>6742274925</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>69200</v>
       </c>
       <c r="Q5" t="n">
-        <v>94500</v>
+        <v>24150</v>
       </c>
       <c r="R5" t="n">
-        <v>400000</v>
+        <v>-11000</v>
       </c>
       <c r="S5" t="n">
-        <v>-408000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 논쟁 및 시장 비판 언급. 반도체 시장 및 국장 상황에 대한 부정적 전망.</t>
+          <t>HLB 그룹 회장 발언 및 Class1 발표에 대한 기대와 불확실성. 담관암 FDA 승인 이슈에 따른 주가 반응 주시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '국장', '시장']</t>
+          <t>['Class1', 'FDA 승인', '담관암']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14390</v>
+        <v>14270</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-3.75%</t>
+          <t>'-4.55%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H6" t="n">
         <v>9.779999999999999</v>
@@ -972,13 +972,13 @@
         <v>14940</v>
       </c>
       <c r="M6" t="n">
-        <v>14290</v>
+        <v>14270</v>
       </c>
       <c r="N6" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>9536144335</v>
+        <v>10521024110</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치적 메시지와 함께 대차, 공매도, 주가 조작 등 시장 관련 의혹 제기. 3분기 실적 기대감 일부 존재.</t>
+          <t>3분기 실적 개선에도 불구하고 정치적 이슈 및 공매도 관련 부정적 언급. 대차 해지 및 마진콜 요구.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['대차', '공매도', '실적']</t>
+          <t>['실적 개선', '공매도', '대차']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1682</v>
+        <v>1649</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-3.78%</t>
+          <t>'-5.66%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="H7" t="n">
         <v>1.77</v>
@@ -1064,13 +1064,13 @@
         <v>1895</v>
       </c>
       <c r="M7" t="n">
-        <v>1661</v>
+        <v>1635</v>
       </c>
       <c r="N7" t="n">
         <v>0.83</v>
       </c>
       <c r="O7" t="n">
-        <v>57071180875</v>
+        <v>59642449222</v>
       </c>
       <c r="P7" t="n">
         <v>2970</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>스페이스X 관련 호재 공시 및 3일간 코스피 수익률 3위 달성. 2연상 기대감 존재.</t>
+          <t>스페이스X 계약 관련 호재 공시로 인한 2연상 이상 기대감. 최근 3일간 코스피 수익률 3위 달성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['스페이스X', '호재', '수익률']</t>
+          <t>['스페이스X', '호재 공시', '2연상']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1209000</v>
+        <v>1199000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-5.32%</t>
+          <t>'-6.11%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="G8" t="n">
-        <v>1576</v>
+        <v>1539</v>
       </c>
       <c r="H8" t="n">
         <v>48.81</v>
@@ -1156,13 +1156,13 @@
         <v>1267000</v>
       </c>
       <c r="M8" t="n">
-        <v>1201000</v>
+        <v>1199000</v>
       </c>
       <c r="N8" t="n">
         <v>48.82</v>
       </c>
       <c r="O8" t="n">
-        <v>1231759068500</v>
+        <v>1354528731500</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 비판 및 솔리다임 상장 철회 요구. 주가 급락에 대한 불만.</t>
+          <t>이재명 및 정부 정책 관련 부정적 언급과 함께 증시 하락에 대한 불만. 반도체 투자 및 솔리다임 상장 관련 우려.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['솔리다임', '정치', '주가']</t>
+          <t>['이재명 리스크', '반도체 투자', '솔리다임']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8960</v>
+        <v>8810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-7.82%</t>
+          <t>'-9.36%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.15</v>
       </c>
       <c r="E9" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="H9" t="n">
         <v>6</v>
@@ -1248,13 +1248,13 @@
         <v>9930</v>
       </c>
       <c r="M9" t="n">
-        <v>8920</v>
+        <v>8810</v>
       </c>
       <c r="N9" t="n">
         <v>6.15</v>
       </c>
       <c r="O9" t="n">
-        <v>8788177330</v>
+        <v>9509560685</v>
       </c>
       <c r="P9" t="n">
         <v>14940</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>테슬라 관련 기대감 및 11000원 돌파 가능성 언급. 거래량 증가 및 공매도 관련 내용 포함.</t>
+          <t>단기 급등 후 하락세 전환에 대한 의구심. 테슬라 관련 기대감 및 공매도 세력과의 공방.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['테슬라', '거래량', '공매도']</t>
+          <t>['테슬라', '공매도', '갭상승']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>73500</v>
+        <v>72200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-10.37%</t>
+          <t>'-11.95%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G10" t="n">
-        <v>239</v>
+        <v>279</v>
       </c>
       <c r="H10" t="n">
         <v>9.380000000000001</v>
@@ -1340,13 +1340,13 @@
         <v>79400</v>
       </c>
       <c r="M10" t="n">
-        <v>73200</v>
+        <v>71600</v>
       </c>
       <c r="N10" t="n">
         <v>9.44</v>
       </c>
       <c r="O10" t="n">
-        <v>45611979200</v>
+        <v>52519906800</v>
       </c>
       <c r="P10" t="n">
         <v>184000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>공매도 비중 및 거래량에 대한 의문 제기. 주가 변동성에 대한 불만과 시장 상황 비판.</t>
+          <t>공매도 물량 증가 및 불확실한 주가 흐름에 대한 불만. 5만 원대 적정가 주장 및 변동성 심화.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', '주가', '거래량']</t>
+          <t>['공매도', '변동성', '적정가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1385,6 +1385,98 @@
       <c r="Z10" t="inlineStr">
         <is>
           <t>272210</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>피노</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>7810</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-12.64%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="E11" t="n">
+        <v>41</v>
+      </c>
+      <c r="F11" t="n">
+        <v>24</v>
+      </c>
+      <c r="G11" t="n">
+        <v>67</v>
+      </c>
+      <c r="H11" t="n">
+        <v>36.01</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>8940</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9010</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7770</v>
+      </c>
+      <c r="N11" t="n">
+        <v>36.39</v>
+      </c>
+      <c r="O11" t="n">
+        <v>11925251260</v>
+      </c>
+      <c r="P11" t="n">
+        <v>19150</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3570</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-110000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>최대 실적 발표에도 불구하고 지속적인 하락세에 대한 실망감. 유증 및 사모펀드 관련 우려.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['유증', '실적', '하한가']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>033790</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261020_10.xlsx
+++ b/data/trending_integrated_20261020_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10870</v>
+        <v>10920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.19%</t>
+          <t>'+19.74%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.86</v>
       </c>
       <c r="E2" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="F2" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G2" t="n">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="H2" t="n">
         <v>0.88</v>
@@ -610,7 +610,7 @@
         <v>1.74</v>
       </c>
       <c r="O2" t="n">
-        <v>147581263145</v>
+        <v>152903441495</v>
       </c>
       <c r="P2" t="n">
         <v>11250</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ESS, 로봇, 이차전지 사업 연관성 및 7천억 규모 수주잔고 기반 1조 시총 달성 기대. 신고가 경신 및 강한 상승세.</t>
+          <t>로봇 사업 강점과 함께 신고가 경신 및 조단위 시총 기대감 표출. 수주 잔고 기반 성장 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇주', '수주잔고', 'ESS']</t>
+          <t>['로봇 사업', '신고가', '수주 잔고']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20150</v>
+        <v>20300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+2.23%</t>
+          <t>'+2.99%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H3" t="n">
         <v>3.07</v>
@@ -702,7 +702,7 @@
         <v>3.32</v>
       </c>
       <c r="O3" t="n">
-        <v>73220190515</v>
+        <v>76354238370</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇 산업 성장과 함께 보안주로서의 중요성 부각. 단기 변동성 속 2만원 안착 여부 주목.</t>
+          <t>보안주로서의 상승 기대감과 외국인 매수세 언급. 다만, 차트 패턴 및 매도 물량에 대한 경계심 공존.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안주', '로봇', '외국인 매수']</t>
+          <t>['보안주', '외국인 매수', '차트 패턴']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>212000</v>
+        <v>42000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-2.75%</t>
+          <t>'-2.21%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>105</v>
       </c>
       <c r="F4" t="n">
-        <v>481</v>
+        <v>74</v>
       </c>
       <c r="G4" t="n">
-        <v>1188</v>
+        <v>542</v>
       </c>
       <c r="H4" t="n">
-        <v>46.04</v>
+        <v>13.11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>218000</v>
+        <v>42950</v>
       </c>
       <c r="K4" t="n">
-        <v>219500</v>
+        <v>42600</v>
       </c>
       <c r="L4" t="n">
-        <v>219500</v>
+        <v>43200</v>
       </c>
       <c r="M4" t="n">
-        <v>211500</v>
+        <v>41550</v>
       </c>
       <c r="N4" t="n">
-        <v>45.99</v>
+        <v>13.04</v>
       </c>
       <c r="O4" t="n">
-        <v>917064036250</v>
+        <v>7282720025</v>
       </c>
       <c r="P4" t="n">
-        <v>374500</v>
+        <v>69200</v>
       </c>
       <c r="Q4" t="n">
-        <v>94500</v>
+        <v>24150</v>
       </c>
       <c r="R4" t="n">
-        <v>400000</v>
+        <v>-11000</v>
       </c>
       <c r="S4" t="n">
-        <v>-408000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부 정책 및 이재명 관련 부정적 언급과 함께 주가 하락세에 대한 우려. 반도체 산업 전망 불확실성.</t>
+          <t>C1(담관암 신약) FDA 승인 발표 기대감 속 주가 변동성 언급. 투자자 간 긍정적/부정적 의견 혼재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['주가 관리', '반도체', '이재명 리스크']</t>
+          <t>['C1', 'FDA 승인', '주가 변동성']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41750</v>
+        <v>212500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-2.79%</t>
+          <t>'-2.52%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>101</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>71</v>
+        <v>503</v>
       </c>
       <c r="G5" t="n">
-        <v>481</v>
+        <v>1034</v>
       </c>
       <c r="H5" t="n">
-        <v>13.11</v>
+        <v>46.04</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>42950</v>
+        <v>218000</v>
       </c>
       <c r="K5" t="n">
-        <v>42600</v>
+        <v>219500</v>
       </c>
       <c r="L5" t="n">
-        <v>43200</v>
+        <v>219500</v>
       </c>
       <c r="M5" t="n">
-        <v>41750</v>
+        <v>210000</v>
       </c>
       <c r="N5" t="n">
-        <v>13.04</v>
+        <v>45.99</v>
       </c>
       <c r="O5" t="n">
-        <v>6742274925</v>
+        <v>1039291469000</v>
       </c>
       <c r="P5" t="n">
-        <v>69200</v>
+        <v>374500</v>
       </c>
       <c r="Q5" t="n">
-        <v>24150</v>
+        <v>94500</v>
       </c>
       <c r="R5" t="n">
-        <v>-11000</v>
+        <v>400000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-408000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>HLB 그룹 회장 발언 및 Class1 발표에 대한 기대와 불확실성. 담관암 FDA 승인 이슈에 따른 주가 반응 주시.</t>
+          <t>정치적 비난과 함께 주가 하락에 대한 불만 표출. 공매도 폐지 및 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['Class1', 'FDA 승인', '담관암']</t>
+          <t>['주가 관리', '공매도', '정치적 비난']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -946,13 +946,13 @@
         <v>0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H6" t="n">
         <v>9.779999999999999</v>
@@ -972,13 +972,13 @@
         <v>14940</v>
       </c>
       <c r="M6" t="n">
-        <v>14270</v>
+        <v>14150</v>
       </c>
       <c r="N6" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>10521024110</v>
+        <v>12100390120</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>3분기 실적 개선에도 불구하고 정치적 이슈 및 공매도 관련 부정적 언급. 대차 해지 및 마진콜 요구.</t>
+          <t>건설 실적 호조에도 불구하고 정치적 이슈 및 공매도 관련 비판 제기. 주가 조작 의혹 및 정책 비판.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적 개선', '공매도', '대차']</t>
+          <t>['건설 실적', '정치적 이슈', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1649</v>
+        <v>17420</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-5.66%</t>
+          <t>'-4.81%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="G7" t="n">
-        <v>210</v>
+        <v>111</v>
       </c>
       <c r="H7" t="n">
-        <v>1.77</v>
+        <v>27.78</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1748</v>
+        <v>18300</v>
       </c>
       <c r="K7" t="n">
-        <v>1706</v>
+        <v>18140</v>
       </c>
       <c r="L7" t="n">
-        <v>1895</v>
+        <v>18140</v>
       </c>
       <c r="M7" t="n">
-        <v>1635</v>
+        <v>17280</v>
       </c>
       <c r="N7" t="n">
-        <v>0.83</v>
+        <v>27.85</v>
       </c>
       <c r="O7" t="n">
-        <v>59642449222</v>
+        <v>20956635155</v>
       </c>
       <c r="P7" t="n">
-        <v>2970</v>
+        <v>35350</v>
       </c>
       <c r="Q7" t="n">
-        <v>890</v>
+        <v>17210</v>
       </c>
       <c r="R7" t="n">
-        <v>-149000</v>
+        <v>-148000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-117000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>스페이스X 계약 관련 호재 공시로 인한 2연상 이상 기대감. 최근 3일간 코스피 수익률 3위 달성.</t>
+          <t>조선업종 전반의 부진 속에서 주가 하락에 대한 우려 표출. 투자 심리 위축 및 52주 최저가 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['스페이스X', '호재 공시', '2연상']</t>
+          <t>['조선업', '주가 하락', '투자 심리']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1199000</v>
+        <v>2550</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-6.11%</t>
+          <t>'-5.38%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>0.34</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>43</v>
       </c>
       <c r="F8" t="n">
-        <v>590</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>1539</v>
+        <v>109</v>
       </c>
       <c r="H8" t="n">
-        <v>48.81</v>
+        <v>1.14</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1277000</v>
+        <v>2695</v>
       </c>
       <c r="K8" t="n">
-        <v>1265000</v>
+        <v>2645</v>
       </c>
       <c r="L8" t="n">
-        <v>1267000</v>
+        <v>2715</v>
       </c>
       <c r="M8" t="n">
-        <v>1199000</v>
+        <v>2510</v>
       </c>
       <c r="N8" t="n">
-        <v>48.82</v>
+        <v>0.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1354528731500</v>
+        <v>23264374598</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>2755</v>
       </c>
       <c r="Q8" t="n">
-        <v>465500</v>
+        <v>865</v>
       </c>
       <c r="R8" t="n">
-        <v>-136000</v>
+        <v>297000</v>
       </c>
       <c r="S8" t="n">
-        <v>-76000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>이재명 및 정부 정책 관련 부정적 언급과 함께 증시 하락에 대한 불만. 반도체 투자 및 솔리다임 상장 관련 우려.</t>
+          <t>하이브리드 부품 수주 사실 기반 주가 상승 기대감 표출. 실적 개선 및 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['이재명 리스크', '반도체 투자', '솔리다임']</t>
+          <t>['하이브리드 부품', '수주', '실적 개선']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8810</v>
+        <v>1203000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-9.36%</t>
+          <t>'-5.79%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.15</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>51</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>622</v>
       </c>
       <c r="G9" t="n">
-        <v>123</v>
+        <v>1554</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>48.81</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>9720</v>
+        <v>1277000</v>
       </c>
       <c r="K9" t="n">
-        <v>9930</v>
+        <v>1265000</v>
       </c>
       <c r="L9" t="n">
-        <v>9930</v>
+        <v>1267000</v>
       </c>
       <c r="M9" t="n">
-        <v>8810</v>
+        <v>1183000</v>
       </c>
       <c r="N9" t="n">
-        <v>6.15</v>
+        <v>48.82</v>
       </c>
       <c r="O9" t="n">
-        <v>9509560685</v>
+        <v>1544917703500</v>
       </c>
       <c r="P9" t="n">
-        <v>14940</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>5390</v>
+        <v>465500</v>
       </c>
       <c r="R9" t="n">
-        <v>-248000</v>
+        <v>-136000</v>
       </c>
       <c r="S9" t="n">
-        <v>-98000</v>
+        <v>-76000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>단기 급등 후 하락세 전환에 대한 의구심. 테슬라 관련 기대감 및 공매도 세력과의 공방.</t>
+          <t>정치적 이슈와 연계하여 주가 급락에 대한 강한 불만 제기. 정부 정책 비판 및 개인 투자자 손실 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['테슬라', '공매도', '갭상승']</t>
+          <t>['이재명 리스크', '주가 급락', '정부 정책']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72200</v>
+        <v>1640</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-11.95%</t>
+          <t>'-6.18%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.06</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="F10" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G10" t="n">
-        <v>279</v>
+        <v>215</v>
       </c>
       <c r="H10" t="n">
-        <v>9.380000000000001</v>
+        <v>1.77</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>82000</v>
+        <v>1748</v>
       </c>
       <c r="K10" t="n">
-        <v>79400</v>
+        <v>1706</v>
       </c>
       <c r="L10" t="n">
-        <v>79400</v>
+        <v>1895</v>
       </c>
       <c r="M10" t="n">
-        <v>71600</v>
+        <v>1630</v>
       </c>
       <c r="N10" t="n">
-        <v>9.44</v>
+        <v>0.83</v>
       </c>
       <c r="O10" t="n">
-        <v>52519906800</v>
+        <v>60800879157</v>
       </c>
       <c r="P10" t="n">
-        <v>184000</v>
+        <v>2970</v>
       </c>
       <c r="Q10" t="n">
-        <v>44750</v>
+        <v>890</v>
       </c>
       <c r="R10" t="n">
-        <v>-225000</v>
+        <v>-149000</v>
       </c>
       <c r="S10" t="n">
-        <v>-35000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>공매도 물량 증가 및 불확실한 주가 흐름에 대한 불만. 5만 원대 적정가 주장 및 변동성 심화.</t>
+          <t>스페이스X 계약 관련 호재 공시로 인한 2연상 이상 기대감. 최근 3일간 코스피 수익률 3위 달성.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', '변동성', '적정가']</t>
+          <t>['스페이스X', '호재 공시', '2연상']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,99 +1384,283 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7810</v>
+        <v>8830</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-12.64%</t>
+          <t>'-9.16%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.38</v>
+        <v>-0.15</v>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="H11" t="n">
-        <v>36.01</v>
+        <v>6</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8940</v>
+        <v>9720</v>
       </c>
       <c r="K11" t="n">
-        <v>9000</v>
+        <v>9930</v>
       </c>
       <c r="L11" t="n">
-        <v>9010</v>
+        <v>9930</v>
       </c>
       <c r="M11" t="n">
-        <v>7770</v>
+        <v>8750</v>
       </c>
       <c r="N11" t="n">
-        <v>36.39</v>
+        <v>6.15</v>
       </c>
       <c r="O11" t="n">
-        <v>11925251260</v>
+        <v>10234027815</v>
       </c>
       <c r="P11" t="n">
-        <v>19150</v>
+        <v>14940</v>
       </c>
       <c r="Q11" t="n">
-        <v>3570</v>
+        <v>5390</v>
       </c>
       <c r="R11" t="n">
-        <v>-110000</v>
+        <v>-248000</v>
       </c>
       <c r="S11" t="n">
-        <v>-5000</v>
+        <v>-98000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>최대 실적 발표에도 불구하고 지속적인 하락세에 대한 실망감. 유증 및 사모펀드 관련 우려.</t>
+          <t>단기 급등 후 하락세 전환에 대한 의구심. 테슬라 관련 기대감 및 공매도 세력과의 공방.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['테슬라', '공매도', '갭상승']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>009900</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>피노</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7890</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-11.74%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="E12" t="n">
+        <v>44</v>
+      </c>
+      <c r="F12" t="n">
+        <v>25</v>
+      </c>
+      <c r="G12" t="n">
+        <v>77</v>
+      </c>
+      <c r="H12" t="n">
+        <v>36.01</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>8940</v>
+      </c>
+      <c r="K12" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>9010</v>
+      </c>
+      <c r="M12" t="n">
+        <v>7750</v>
+      </c>
+      <c r="N12" t="n">
+        <v>36.39</v>
+      </c>
+      <c r="O12" t="n">
+        <v>13041969415</v>
+      </c>
+      <c r="P12" t="n">
+        <v>19150</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3570</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-110000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>최대 실적에도 불구하고 주가 하락에 대한 불만 제기. 유증 및 사모펀드 관련 우려 표출.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
         <v>0.2</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>['유증', '실적', '하한가']</t>
-        </is>
-      </c>
-      <c r="X11" t="n">
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['최대 실적', '주가 하락', '유상증자']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
         <v>1</v>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>033790</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>한화시스템</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>71500</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>'-12.80%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E13" t="n">
+        <v>99</v>
+      </c>
+      <c r="F13" t="n">
+        <v>59</v>
+      </c>
+      <c r="G13" t="n">
+        <v>310</v>
+      </c>
+      <c r="H13" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>82000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>79400</v>
+      </c>
+      <c r="L13" t="n">
+        <v>79400</v>
+      </c>
+      <c r="M13" t="n">
+        <v>71100</v>
+      </c>
+      <c r="N13" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="O13" t="n">
+        <v>56787968400</v>
+      </c>
+      <c r="P13" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>44750</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-225000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-35000</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>공매도 및 정치적 이슈와 연계하여 주가 하락에 대한 불만 제기. 정부 정책 비판 및 투자 심리 위축.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['공매도', '주가 하락', '정부 정책']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>272210</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261020_10.xlsx
+++ b/data/trending_integrated_20261020_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10920</v>
+        <v>10790</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.74%</t>
+          <t>'+18.31%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.86</v>
       </c>
       <c r="E2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F2" t="n">
         <v>83</v>
       </c>
       <c r="G2" t="n">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="H2" t="n">
         <v>0.88</v>
@@ -610,7 +610,7 @@
         <v>1.74</v>
       </c>
       <c r="O2" t="n">
-        <v>152903441495</v>
+        <v>157761574230</v>
       </c>
       <c r="P2" t="n">
         <v>11250</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>로봇 사업 강점과 함께 신고가 경신 및 조단위 시총 기대감 표출. 수주 잔고 기반 성장 전망.</t>
+          <t>로봇, ESS, 이차전지 사업 연관성 및 7천억 규모 수주잔고 기반 1조원 시총 기대감. 신고가 및 급등세.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇 사업', '신고가', '수주 잔고']</t>
+          <t>['로봇', '수주잔고', '신고가']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20300</v>
+        <v>74600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+2.99%</t>
+          <t>'+15.66%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.25</v>
+        <v>0.29</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="H3" t="n">
-        <v>3.07</v>
+        <v>5.95</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>19710</v>
+        <v>64500</v>
       </c>
       <c r="K3" t="n">
-        <v>19450</v>
+        <v>68000</v>
       </c>
       <c r="L3" t="n">
-        <v>21850</v>
+        <v>74600</v>
       </c>
       <c r="M3" t="n">
-        <v>19450</v>
+        <v>66700</v>
       </c>
       <c r="N3" t="n">
-        <v>3.32</v>
+        <v>5.66</v>
       </c>
       <c r="O3" t="n">
-        <v>76354238370</v>
+        <v>69834281900</v>
       </c>
       <c r="P3" t="n">
-        <v>22450</v>
+        <v>148300</v>
       </c>
       <c r="Q3" t="n">
-        <v>6320</v>
+        <v>17780</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-52000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>보안주로서의 상승 기대감과 외국인 매수세 언급. 다만, 차트 패턴 및 매도 물량에 대한 경계심 공존.</t>
+          <t>반도체 소부장 섹터 강세 속 상대적 선방 및 상승세. 지수 하락 속 견조한 흐름.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안주', '외국인 매수', '차트 패턴']</t>
+          <t>['반도체', '소부장', '상승세']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42000</v>
+        <v>20100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-2.21%</t>
+          <t>'+1.98%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.25</v>
       </c>
       <c r="E4" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>542</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>13.11</v>
+        <v>3.07</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>42950</v>
+        <v>19710</v>
       </c>
       <c r="K4" t="n">
-        <v>42600</v>
+        <v>19450</v>
       </c>
       <c r="L4" t="n">
-        <v>43200</v>
+        <v>21850</v>
       </c>
       <c r="M4" t="n">
-        <v>41550</v>
+        <v>19450</v>
       </c>
       <c r="N4" t="n">
-        <v>13.04</v>
+        <v>3.32</v>
       </c>
       <c r="O4" t="n">
-        <v>7282720025</v>
+        <v>77392143420</v>
       </c>
       <c r="P4" t="n">
-        <v>69200</v>
+        <v>22450</v>
       </c>
       <c r="Q4" t="n">
-        <v>24150</v>
+        <v>6320</v>
       </c>
       <c r="R4" t="n">
-        <v>-11000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>C1(담관암 신약) FDA 승인 발표 기대감 속 주가 변동성 언급. 투자자 간 긍정적/부정적 의견 혼재.</t>
+          <t>로봇 섹터 강세 속 보안주의 중요성 언급, 단기 급등 후 차익실현 매물 출회. 개미 무덤 차트 형성 우려.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['C1', 'FDA 승인', '주가 변동성']</t>
+          <t>['보안주', '로봇', '차익실현']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>212500</v>
+        <v>215000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-2.52%</t>
+          <t>'-1.38%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="G5" t="n">
-        <v>1034</v>
+        <v>1134</v>
       </c>
       <c r="H5" t="n">
         <v>46.04</v>
@@ -886,7 +886,7 @@
         <v>45.99</v>
       </c>
       <c r="O5" t="n">
-        <v>1039291469000</v>
+        <v>1103541544500</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 비난과 함께 주가 하락에 대한 불만 표출. 공매도 폐지 및 정부 정책 비판.</t>
+          <t>현 정부의 주가 관리 부재 및 경제 상황에 대한 부정적 평가. 국내 증시 하락세 속 부진.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['주가 관리', '공매도', '정치적 비난']</t>
+          <t>['주가 관리', '경제 상황', '하락세']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14270</v>
+        <v>42250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-4.55%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="G6" t="n">
-        <v>126</v>
+        <v>589</v>
       </c>
       <c r="H6" t="n">
-        <v>9.779999999999999</v>
+        <v>13.11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14950</v>
+        <v>42950</v>
       </c>
       <c r="K6" t="n">
-        <v>14610</v>
+        <v>42600</v>
       </c>
       <c r="L6" t="n">
-        <v>14940</v>
+        <v>43200</v>
       </c>
       <c r="M6" t="n">
-        <v>14150</v>
+        <v>41550</v>
       </c>
       <c r="N6" t="n">
-        <v>9.699999999999999</v>
+        <v>13.04</v>
       </c>
       <c r="O6" t="n">
-        <v>12100390120</v>
+        <v>7946688025</v>
       </c>
       <c r="P6" t="n">
-        <v>40350</v>
+        <v>69200</v>
       </c>
       <c r="Q6" t="n">
-        <v>3320</v>
+        <v>24150</v>
       </c>
       <c r="R6" t="n">
-        <v>-45000</v>
+        <v>-11000</v>
       </c>
       <c r="S6" t="n">
-        <v>-37000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>건설 실적 호조에도 불구하고 정치적 이슈 및 공매도 관련 비판 제기. 주가 조작 의혹 및 정책 비판.</t>
+          <t>담관암 FDA 승인 관련 불확실성 속 주가 부양 기대감 존재. Class1 발표 여부에 따라 주가 방향성 결정 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['건설 실적', '정치적 이슈', '공매도']</t>
+          <t>['FDA 승인', 'Class1 발표', '주가 부양']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17420</v>
+        <v>17700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-4.81%</t>
+          <t>'-3.28%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H7" t="n">
         <v>27.78</v>
@@ -1070,7 +1070,7 @@
         <v>27.85</v>
       </c>
       <c r="O7" t="n">
-        <v>20956635155</v>
+        <v>21890610030</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2550</v>
+        <v>14460</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-5.38%</t>
+          <t>'-3.28%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="E8" t="n">
+        <v>76</v>
+      </c>
+      <c r="F8" t="n">
         <v>43</v>
       </c>
-      <c r="F8" t="n">
-        <v>31</v>
-      </c>
       <c r="G8" t="n">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="H8" t="n">
-        <v>1.14</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2695</v>
+        <v>14950</v>
       </c>
       <c r="K8" t="n">
-        <v>2645</v>
+        <v>14610</v>
       </c>
       <c r="L8" t="n">
-        <v>2715</v>
+        <v>14940</v>
       </c>
       <c r="M8" t="n">
-        <v>2510</v>
+        <v>14150</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>23264374598</v>
+        <v>12715281190</v>
       </c>
       <c r="P8" t="n">
-        <v>2755</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>865</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>297000</v>
+        <v>-45000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-37000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>하이브리드 부품 수주 사실 기반 주가 상승 기대감 표출. 실적 개선 및 긍정적 전망 제시.</t>
+          <t>3분기 실적 호조에도 불구하고 정치적 이슈와 공매도, 대차 문제로 인한 주가 하락 압력 지속. 주주 행동 촉구.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['하이브리드 부품', '수주', '실적 개선']</t>
+          <t>['실적 호조', '공매도', '대차 해지']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1203000</v>
+        <v>1219000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-5.79%</t>
+          <t>'-4.54%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="G9" t="n">
-        <v>1554</v>
+        <v>1561</v>
       </c>
       <c r="H9" t="n">
         <v>48.81</v>
@@ -1254,7 +1254,7 @@
         <v>48.82</v>
       </c>
       <c r="O9" t="n">
-        <v>1544917703500</v>
+        <v>1664871894000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계하여 주가 급락에 대한 강한 불만 제기. 정부 정책 비판 및 개인 투자자 손실 우려.</t>
+          <t>정부 정책 및 정치적 이슈와 연계된 주가 하락에 대한 불만. '이재명 리스크' 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['이재명 리스크', '주가 급락', '정부 정책']</t>
+          <t>['이재명 리스크', '주가 하락', '정부 정책']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,70 +1299,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1640</v>
+        <v>2565</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-6.18%</t>
+          <t>'-4.82%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.34</v>
       </c>
       <c r="E10" t="n">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="F10" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>215</v>
+        <v>138</v>
       </c>
       <c r="H10" t="n">
-        <v>1.77</v>
+        <v>1.14</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1748</v>
+        <v>2695</v>
       </c>
       <c r="K10" t="n">
-        <v>1706</v>
+        <v>2645</v>
       </c>
       <c r="L10" t="n">
-        <v>1895</v>
+        <v>2715</v>
       </c>
       <c r="M10" t="n">
-        <v>1630</v>
+        <v>2510</v>
       </c>
       <c r="N10" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="O10" t="n">
-        <v>60800879157</v>
+        <v>24342222826</v>
       </c>
       <c r="P10" t="n">
-        <v>2970</v>
+        <v>2755</v>
       </c>
       <c r="Q10" t="n">
-        <v>890</v>
+        <v>865</v>
       </c>
       <c r="R10" t="n">
-        <v>-149000</v>
+        <v>297000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>스페이스X 계약 관련 호재 공시로 인한 2연상 이상 기대감. 최근 3일간 코스피 수익률 3위 달성.</t>
+          <t>1000억원 규모 하이브리드 부품 수주 공시 및 역대급 3분기 실적 기대감. 주가 상승 및 매수 기회 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['스페이스X', '호재 공시', '2연상']</t>
+          <t>['하이브리드 부품', '수주', '실적']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8830</v>
+        <v>1658</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-9.16%</t>
+          <t>'-5.15%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="G11" t="n">
-        <v>126</v>
+        <v>228</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>1.77</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>9720</v>
+        <v>1748</v>
       </c>
       <c r="K11" t="n">
-        <v>9930</v>
+        <v>1706</v>
       </c>
       <c r="L11" t="n">
-        <v>9930</v>
+        <v>1895</v>
       </c>
       <c r="M11" t="n">
-        <v>8750</v>
+        <v>1625</v>
       </c>
       <c r="N11" t="n">
-        <v>6.15</v>
+        <v>0.83</v>
       </c>
       <c r="O11" t="n">
-        <v>10234027815</v>
+        <v>61819810672</v>
       </c>
       <c r="P11" t="n">
-        <v>14940</v>
+        <v>2970</v>
       </c>
       <c r="Q11" t="n">
-        <v>5390</v>
+        <v>890</v>
       </c>
       <c r="R11" t="n">
-        <v>-248000</v>
+        <v>-149000</v>
       </c>
       <c r="S11" t="n">
-        <v>-98000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>단기 급등 후 하락세 전환에 대한 의구심. 테슬라 관련 기대감 및 공매도 세력과의 공방.</t>
+          <t>스페이스X 관련 호재 공시로 인한 급등세 및 2연상 이상 기대감. 최근 3일간 코스피 수익률 3위 기록.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['테슬라', '공매도', '갭상승']</t>
+          <t>['스페이스X', '호재', '상한가']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,86 +1476,86 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7890</v>
+        <v>32100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-11.74%</t>
+          <t>'-5.45%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.38</v>
+        <v>-0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="H12" t="n">
-        <v>36.01</v>
+        <v>12.79</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>8940</v>
+        <v>33950</v>
       </c>
       <c r="K12" t="n">
-        <v>9000</v>
+        <v>33250</v>
       </c>
       <c r="L12" t="n">
-        <v>9010</v>
+        <v>34150</v>
       </c>
       <c r="M12" t="n">
-        <v>7750</v>
+        <v>31300</v>
       </c>
       <c r="N12" t="n">
-        <v>36.39</v>
+        <v>12.81</v>
       </c>
       <c r="O12" t="n">
-        <v>13041969415</v>
+        <v>33868943525</v>
       </c>
       <c r="P12" t="n">
-        <v>19150</v>
+        <v>59300</v>
       </c>
       <c r="Q12" t="n">
-        <v>3570</v>
+        <v>22000</v>
       </c>
       <c r="R12" t="n">
-        <v>-110000</v>
+        <v>-108000</v>
       </c>
       <c r="S12" t="n">
-        <v>-5000</v>
+        <v>-12000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>최대 실적에도 불구하고 주가 하락에 대한 불만 제기. 유증 및 사모펀드 관련 우려 표출.</t>
+          <t>미국 태양광 관세 관련 승리 및 중간선거 결과에 따른 기대감. 매수 기회 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['최대 실적', '주가 하락', '유상증자']</t>
+          <t>['태양광', '미국 관세', '중간선거']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>71500</v>
+        <v>8900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-12.80%</t>
+          <t>'-8.44%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.06</v>
+        <v>-0.15</v>
       </c>
       <c r="E13" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="F13" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>310</v>
+        <v>141</v>
       </c>
       <c r="H13" t="n">
-        <v>9.380000000000001</v>
+        <v>6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,58 +1607,242 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>82000</v>
+        <v>9720</v>
       </c>
       <c r="K13" t="n">
-        <v>79400</v>
+        <v>9930</v>
       </c>
       <c r="L13" t="n">
-        <v>79400</v>
+        <v>9930</v>
       </c>
       <c r="M13" t="n">
-        <v>71100</v>
+        <v>8750</v>
       </c>
       <c r="N13" t="n">
-        <v>9.44</v>
+        <v>6.15</v>
       </c>
       <c r="O13" t="n">
-        <v>56787968400</v>
+        <v>10658847405</v>
       </c>
       <c r="P13" t="n">
-        <v>184000</v>
+        <v>14940</v>
       </c>
       <c r="Q13" t="n">
-        <v>44750</v>
+        <v>5390</v>
       </c>
       <c r="R13" t="n">
-        <v>-225000</v>
+        <v>-248000</v>
       </c>
       <c r="S13" t="n">
-        <v>-35000</v>
+        <v>-98000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공매도 및 정치적 이슈와 연계하여 주가 하락에 대한 불만 제기. 정부 정책 비판 및 투자 심리 위축.</t>
+          <t>급등 후 하락, 고밸류 부담 속 지수 영향 및 공매도 공방. 테슬라 관련 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['고밸류', '공매도', '테슬라']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>009900</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>피노</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'-10.51%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="E14" t="n">
+        <v>46</v>
+      </c>
+      <c r="F14" t="n">
+        <v>25</v>
+      </c>
+      <c r="G14" t="n">
+        <v>81</v>
+      </c>
+      <c r="H14" t="n">
+        <v>36.01</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>8940</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>9010</v>
+      </c>
+      <c r="M14" t="n">
+        <v>7750</v>
+      </c>
+      <c r="N14" t="n">
+        <v>36.39</v>
+      </c>
+      <c r="O14" t="n">
+        <v>13567873625</v>
+      </c>
+      <c r="P14" t="n">
+        <v>19150</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3570</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-110000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>최대 실적 발표에도 불구하고 하락세 지속. 유증, RCPS 조달 조건 등에 대한 부정적 평가. 투경 지정.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
         <v>0.1</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>['공매도', '주가 하락', '정부 정책']</t>
-        </is>
-      </c>
-      <c r="X13" t="n">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['유증', '최대 실적', '투경']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
         <v>1</v>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>033790</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>한화시스템</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>72100</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'-12.07%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E15" t="n">
+        <v>115</v>
+      </c>
+      <c r="F15" t="n">
+        <v>70</v>
+      </c>
+      <c r="G15" t="n">
+        <v>354</v>
+      </c>
+      <c r="H15" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>82000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>79400</v>
+      </c>
+      <c r="L15" t="n">
+        <v>79400</v>
+      </c>
+      <c r="M15" t="n">
+        <v>71100</v>
+      </c>
+      <c r="N15" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="O15" t="n">
+        <v>60450661900</v>
+      </c>
+      <c r="P15" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>44750</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-225000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-35000</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>공매도 비중 증가와 함께 주가 급락. 전작권 관련 호재 해석 여부 불확실, 매수 기회 제공 가능성 시사.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['공매도', '전작권', '주가 급락']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>272210</t>
         </is>

--- a/data/trending_integrated_20261020_10.xlsx
+++ b/data/trending_integrated_20261020_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10790</v>
+        <v>76500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.31%</t>
+          <t>'+18.60%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.86</v>
+        <v>0.29</v>
       </c>
       <c r="E2" t="n">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="F2" t="n">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="H2" t="n">
-        <v>0.88</v>
+        <v>5.95</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9120</v>
+        <v>64500</v>
       </c>
       <c r="K2" t="n">
-        <v>9500</v>
+        <v>68000</v>
       </c>
       <c r="L2" t="n">
-        <v>11250</v>
+        <v>76700</v>
       </c>
       <c r="M2" t="n">
-        <v>9470</v>
+        <v>66700</v>
       </c>
       <c r="N2" t="n">
-        <v>1.74</v>
+        <v>5.66</v>
       </c>
       <c r="O2" t="n">
-        <v>157761574230</v>
+        <v>76007258850</v>
       </c>
       <c r="P2" t="n">
-        <v>11250</v>
+        <v>148300</v>
       </c>
       <c r="Q2" t="n">
-        <v>2270</v>
+        <v>17780</v>
       </c>
       <c r="R2" t="n">
-        <v>405000</v>
+        <v>-52000</v>
       </c>
       <c r="S2" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>로봇, ESS, 이차전지 사업 연관성 및 7천억 규모 수주잔고 기반 1조원 시총 기대감. 신고가 및 급등세.</t>
+          <t>반도체 관련주로서 지수 하락에도 불구하고 강한 상승세 기록. 2차전지 및 반도체 소부장 테마 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇', '수주잔고', '신고가']</t>
+          <t>['반도체', '상승세', '테마 기대감']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74600</v>
+        <v>10670</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.66%</t>
+          <t>'+17.00%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.29</v>
+        <v>-0.86</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>119</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="G3" t="n">
-        <v>75</v>
+        <v>291</v>
       </c>
       <c r="H3" t="n">
-        <v>5.95</v>
+        <v>0.88</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>64500</v>
+        <v>9120</v>
       </c>
       <c r="K3" t="n">
-        <v>68000</v>
+        <v>9500</v>
       </c>
       <c r="L3" t="n">
-        <v>74600</v>
+        <v>11250</v>
       </c>
       <c r="M3" t="n">
-        <v>66700</v>
+        <v>9470</v>
       </c>
       <c r="N3" t="n">
-        <v>5.66</v>
+        <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>69834281900</v>
+        <v>163268324590</v>
       </c>
       <c r="P3" t="n">
-        <v>148300</v>
+        <v>11250</v>
       </c>
       <c r="Q3" t="n">
-        <v>17780</v>
+        <v>2270</v>
       </c>
       <c r="R3" t="n">
-        <v>-52000</v>
+        <v>405000</v>
       </c>
       <c r="S3" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>반도체 소부장 섹터 강세 속 상대적 선방 및 상승세. 지수 하락 속 견조한 흐름.</t>
+          <t>로봇 사업 성장 기대감 및 7천억 원 수주 잔고 확보. 신고가 경신 및 1조 클럽 목표.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체', '소부장', '상승세']</t>
+          <t>['로봇 사업', '수주 잔고', '신고가']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
@@ -762,13 +762,13 @@
         <v>-0.25</v>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H4" t="n">
         <v>3.07</v>
@@ -794,7 +794,7 @@
         <v>3.32</v>
       </c>
       <c r="O4" t="n">
-        <v>77392143420</v>
+        <v>79348097550</v>
       </c>
       <c r="P4" t="n">
         <v>22450</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 섹터 강세 속 보안주의 중요성 언급, 단기 급등 후 차익실현 매물 출회. 개미 무덤 차트 형성 우려.</t>
+          <t>로봇주 상승에 따른 보안주 동반 상승 기대감 속에서 변동성 확대 및 털기 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['보안주', '로봇', '차익실현']</t>
+          <t>['로봇주', '보안주', '변동성']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,83 +839,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>215000</v>
+        <v>42400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-1.38%</t>
+          <t>'-1.28%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>116</v>
       </c>
       <c r="F5" t="n">
-        <v>499</v>
+        <v>81</v>
       </c>
       <c r="G5" t="n">
-        <v>1134</v>
+        <v>705</v>
       </c>
       <c r="H5" t="n">
-        <v>46.04</v>
+        <v>13.11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>218000</v>
+        <v>42950</v>
       </c>
       <c r="K5" t="n">
-        <v>219500</v>
+        <v>42600</v>
       </c>
       <c r="L5" t="n">
-        <v>219500</v>
+        <v>43200</v>
       </c>
       <c r="M5" t="n">
-        <v>210000</v>
+        <v>41550</v>
       </c>
       <c r="N5" t="n">
-        <v>45.99</v>
+        <v>13.04</v>
       </c>
       <c r="O5" t="n">
-        <v>1103541544500</v>
+        <v>8185377900</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>69200</v>
       </c>
       <c r="Q5" t="n">
-        <v>94500</v>
+        <v>24150</v>
       </c>
       <c r="R5" t="n">
-        <v>400000</v>
+        <v>-11000</v>
       </c>
       <c r="S5" t="n">
-        <v>-408000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>현 정부의 주가 관리 부재 및 경제 상황에 대한 부정적 평가. 국내 증시 하락세 속 부진.</t>
+          <t>C1 발표 및 담관암 FDA 승인 기대감 속에서 주가 횡보 및 추매 의견.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['주가 관리', '경제 상황', '하락세']</t>
+          <t>['C1 발표', 'FDA 승인', '추매']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42250</v>
+        <v>214500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.63%</t>
+          <t>'-1.61%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>111</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>79</v>
+        <v>507</v>
       </c>
       <c r="G6" t="n">
-        <v>589</v>
+        <v>1142</v>
       </c>
       <c r="H6" t="n">
-        <v>13.11</v>
+        <v>46.04</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>42950</v>
+        <v>218000</v>
       </c>
       <c r="K6" t="n">
-        <v>42600</v>
+        <v>219500</v>
       </c>
       <c r="L6" t="n">
-        <v>43200</v>
+        <v>219500</v>
       </c>
       <c r="M6" t="n">
-        <v>41550</v>
+        <v>210000</v>
       </c>
       <c r="N6" t="n">
-        <v>13.04</v>
+        <v>45.99</v>
       </c>
       <c r="O6" t="n">
-        <v>7946688025</v>
+        <v>1149646197750</v>
       </c>
       <c r="P6" t="n">
-        <v>69200</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>24150</v>
+        <v>94500</v>
       </c>
       <c r="R6" t="n">
-        <v>-11000</v>
+        <v>400000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-408000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>담관암 FDA 승인 관련 불확실성 속 주가 부양 기대감 존재. Class1 발표 여부에 따라 주가 방향성 결정 전망.</t>
+          <t>정부 정책에 대한 불만과 증시 부진에 대한 부정적인 게시글 다수.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['FDA 승인', 'Class1 발표', '주가 부양']</t>
+          <t>['정부 정책', '증시 부진', '불만']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17700</v>
+        <v>7310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-3.28%</t>
+          <t>'-2.01%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="H7" t="n">
-        <v>27.78</v>
+        <v>25.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18300</v>
+        <v>7460</v>
       </c>
       <c r="K7" t="n">
-        <v>18140</v>
+        <v>7410</v>
       </c>
       <c r="L7" t="n">
-        <v>18140</v>
+        <v>7490</v>
       </c>
       <c r="M7" t="n">
-        <v>17280</v>
+        <v>7200</v>
       </c>
       <c r="N7" t="n">
-        <v>27.85</v>
+        <v>25.42</v>
       </c>
       <c r="O7" t="n">
-        <v>21890610030</v>
+        <v>6806015085</v>
       </c>
       <c r="P7" t="n">
-        <v>35350</v>
+        <v>17950</v>
       </c>
       <c r="Q7" t="n">
-        <v>17210</v>
+        <v>7190</v>
       </c>
       <c r="R7" t="n">
-        <v>-148000</v>
+        <v>-77000</v>
       </c>
       <c r="S7" t="n">
-        <v>-117000</v>
+        <v>-15000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>조선업종 전반의 부진 속에서 주가 하락에 대한 우려 표출. 투자 심리 위축 및 52주 최저가 언급.</t>
+          <t>실적 발표 후에도 주가 하락세 지속 및 외인 수급 부진에 대한 우려.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['조선업', '주가 하락', '투자 심리']</t>
+          <t>['실적 부진', '외인 수급', '주가 하락']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14460</v>
+        <v>17660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-3.28%</t>
+          <t>'-3.50%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="H8" t="n">
-        <v>9.779999999999999</v>
+        <v>27.78</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14950</v>
+        <v>18300</v>
       </c>
       <c r="K8" t="n">
-        <v>14610</v>
+        <v>18140</v>
       </c>
       <c r="L8" t="n">
-        <v>14940</v>
+        <v>18140</v>
       </c>
       <c r="M8" t="n">
-        <v>14150</v>
+        <v>17280</v>
       </c>
       <c r="N8" t="n">
-        <v>9.699999999999999</v>
+        <v>27.85</v>
       </c>
       <c r="O8" t="n">
-        <v>12715281190</v>
+        <v>22608360195</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>17210</v>
       </c>
       <c r="R8" t="n">
-        <v>-45000</v>
+        <v>-148000</v>
       </c>
       <c r="S8" t="n">
-        <v>-37000</v>
+        <v>-117000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3분기 실적 호조에도 불구하고 정치적 이슈와 공매도, 대차 문제로 인한 주가 하락 압력 지속. 주주 행동 촉구.</t>
+          <t>조선업 부진 및 반도체 관련 종목 동반 하락 우려 속에서 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['실적 호조', '공매도', '대차 해지']</t>
+          <t>['조선업 부진', '반도체 하락', '주가 하락']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1219000</v>
+        <v>14410</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-4.54%</t>
+          <t>'-3.61%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>78</v>
       </c>
       <c r="F9" t="n">
-        <v>625</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>1561</v>
+        <v>135</v>
       </c>
       <c r="H9" t="n">
-        <v>48.81</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1277000</v>
+        <v>14950</v>
       </c>
       <c r="K9" t="n">
-        <v>1265000</v>
+        <v>14610</v>
       </c>
       <c r="L9" t="n">
-        <v>1267000</v>
+        <v>14940</v>
       </c>
       <c r="M9" t="n">
-        <v>1183000</v>
+        <v>14150</v>
       </c>
       <c r="N9" t="n">
-        <v>48.82</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>1664871894000</v>
+        <v>13135517120</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>465500</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>-136000</v>
+        <v>-45000</v>
       </c>
       <c r="S9" t="n">
-        <v>-76000</v>
+        <v>-37000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정부 정책 및 정치적 이슈와 연계된 주가 하락에 대한 불만. '이재명 리스크' 언급.</t>
+          <t>3분기 실적 폭증 기대에도 불구하고 주가 하락. 주가 조작 및 공매도 관련 의혹 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['이재명 리스크', '주가 하락', '정부 정책']</t>
+          <t>['실적', '공매도', '주가조작']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2565</v>
+        <v>1227000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.82%</t>
+          <t>'-3.92%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.34</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>45</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>597</v>
       </c>
       <c r="G10" t="n">
-        <v>138</v>
+        <v>1461</v>
       </c>
       <c r="H10" t="n">
-        <v>1.14</v>
+        <v>48.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2695</v>
+        <v>1277000</v>
       </c>
       <c r="K10" t="n">
-        <v>2645</v>
+        <v>1265000</v>
       </c>
       <c r="L10" t="n">
-        <v>2715</v>
+        <v>1267000</v>
       </c>
       <c r="M10" t="n">
-        <v>2510</v>
+        <v>1183000</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8</v>
+        <v>48.82</v>
       </c>
       <c r="O10" t="n">
-        <v>24342222826</v>
+        <v>1830056517000</v>
       </c>
       <c r="P10" t="n">
-        <v>2755</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>865</v>
+        <v>465500</v>
       </c>
       <c r="R10" t="n">
-        <v>297000</v>
+        <v>-136000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-76000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1000억원 규모 하이브리드 부품 수주 공시 및 역대급 3분기 실적 기대감. 주가 상승 및 매수 기회 언급.</t>
+          <t>정치권의 경제 정책 실패로 인한 주가 하락에 대한 강한 불만과 투자 철회 의견.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['하이브리드 부품', '수주', '실적']</t>
+          <t>['경제 정책 실패', '주가 하락', '정치권 비판']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1658</v>
+        <v>2575</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.15%</t>
+          <t>'-4.45%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.34</v>
       </c>
       <c r="E11" t="n">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="F11" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
-        <v>228</v>
+        <v>138</v>
       </c>
       <c r="H11" t="n">
-        <v>1.77</v>
+        <v>1.14</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1748</v>
+        <v>2695</v>
       </c>
       <c r="K11" t="n">
-        <v>1706</v>
+        <v>2645</v>
       </c>
       <c r="L11" t="n">
-        <v>1895</v>
+        <v>2715</v>
       </c>
       <c r="M11" t="n">
-        <v>1625</v>
+        <v>2510</v>
       </c>
       <c r="N11" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="O11" t="n">
-        <v>61819810672</v>
+        <v>24951381592</v>
       </c>
       <c r="P11" t="n">
-        <v>2970</v>
+        <v>2755</v>
       </c>
       <c r="Q11" t="n">
-        <v>890</v>
+        <v>865</v>
       </c>
       <c r="R11" t="n">
-        <v>-149000</v>
+        <v>297000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>스페이스X 관련 호재 공시로 인한 급등세 및 2연상 이상 기대감. 최근 3일간 코스피 수익률 3위 기록.</t>
+          <t>1000억원 규모 하이브리드 부품 수주 공시 및 역대급 3분기 실적 기대감. 주가 상승 및 매수 기회 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['스페이스X', '호재', '상한가']</t>
+          <t>['하이브리드 부품', '수주', '실적']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32100</v>
+        <v>31950</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.45%</t>
+          <t>'-5.89%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H12" t="n">
         <v>12.79</v>
@@ -1530,7 +1530,7 @@
         <v>12.81</v>
       </c>
       <c r="O12" t="n">
-        <v>33868943525</v>
+        <v>35235122575</v>
       </c>
       <c r="P12" t="n">
         <v>59300</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8900</v>
+        <v>1632</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-8.44%</t>
+          <t>'-6.64%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="G13" t="n">
-        <v>141</v>
+        <v>234</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>1.77</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>9720</v>
+        <v>1748</v>
       </c>
       <c r="K13" t="n">
-        <v>9930</v>
+        <v>1706</v>
       </c>
       <c r="L13" t="n">
-        <v>9930</v>
+        <v>1895</v>
       </c>
       <c r="M13" t="n">
-        <v>8750</v>
+        <v>1625</v>
       </c>
       <c r="N13" t="n">
-        <v>6.15</v>
+        <v>0.83</v>
       </c>
       <c r="O13" t="n">
-        <v>10658847405</v>
+        <v>62417819987</v>
       </c>
       <c r="P13" t="n">
-        <v>14940</v>
+        <v>2970</v>
       </c>
       <c r="Q13" t="n">
-        <v>5390</v>
+        <v>890</v>
       </c>
       <c r="R13" t="n">
-        <v>-248000</v>
+        <v>-149000</v>
       </c>
       <c r="S13" t="n">
-        <v>-98000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>급등 후 하락, 고밸류 부담 속 지수 영향 및 공매도 공방. 테슬라 관련 기대감.</t>
+          <t>스페이스X 계약 체결 관련 호재 공시로 인한 급등세 전망. 최근 3일간 코스피 수익률 3위 달성.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['고밸류', '공매도', '테슬라']</t>
+          <t>['스페이스X', '호재 공시', '급등']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8000</v>
+        <v>8870</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-10.51%</t>
+          <t>'-8.74%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.38</v>
+        <v>-0.15</v>
       </c>
       <c r="E14" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G14" t="n">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="H14" t="n">
-        <v>36.01</v>
+        <v>6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8940</v>
+        <v>9720</v>
       </c>
       <c r="K14" t="n">
-        <v>9000</v>
+        <v>9930</v>
       </c>
       <c r="L14" t="n">
-        <v>9010</v>
+        <v>9930</v>
       </c>
       <c r="M14" t="n">
-        <v>7750</v>
+        <v>8750</v>
       </c>
       <c r="N14" t="n">
-        <v>36.39</v>
+        <v>6.15</v>
       </c>
       <c r="O14" t="n">
-        <v>13567873625</v>
+        <v>11023052735</v>
       </c>
       <c r="P14" t="n">
-        <v>19150</v>
+        <v>14940</v>
       </c>
       <c r="Q14" t="n">
-        <v>3570</v>
+        <v>5390</v>
       </c>
       <c r="R14" t="n">
-        <v>-110000</v>
+        <v>-248000</v>
       </c>
       <c r="S14" t="n">
-        <v>-5000</v>
+        <v>-98000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>최대 실적 발표에도 불구하고 하락세 지속. 유증, RCPS 조달 조건 등에 대한 부정적 평가. 투경 지정.</t>
+          <t>공매도 압력 속에서 변동성 확대 우려 및 단기 매매 관점의 게시글.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['유증', '최대 실적', '투경']</t>
+          <t>['공매도', '변동성', '단기 매매']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,86 +1752,86 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72100</v>
+        <v>8030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-12.07%</t>
+          <t>'-10.18%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.06</v>
+        <v>-0.38</v>
       </c>
       <c r="E15" t="n">
-        <v>115</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="G15" t="n">
-        <v>354</v>
+        <v>83</v>
       </c>
       <c r="H15" t="n">
-        <v>9.380000000000001</v>
+        <v>36.01</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>82000</v>
+        <v>8940</v>
       </c>
       <c r="K15" t="n">
-        <v>79400</v>
+        <v>9000</v>
       </c>
       <c r="L15" t="n">
-        <v>79400</v>
+        <v>9010</v>
       </c>
       <c r="M15" t="n">
-        <v>71100</v>
+        <v>7750</v>
       </c>
       <c r="N15" t="n">
-        <v>9.44</v>
+        <v>36.39</v>
       </c>
       <c r="O15" t="n">
-        <v>60450661900</v>
+        <v>14270476815</v>
       </c>
       <c r="P15" t="n">
-        <v>184000</v>
+        <v>19150</v>
       </c>
       <c r="Q15" t="n">
-        <v>44750</v>
+        <v>3570</v>
       </c>
       <c r="R15" t="n">
-        <v>-225000</v>
+        <v>-110000</v>
       </c>
       <c r="S15" t="n">
-        <v>-35000</v>
+        <v>-5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>공매도 비중 증가와 함께 주가 급락. 전작권 관련 호재 해석 여부 불확실, 매수 기회 제공 가능성 시사.</t>
+          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도', '전작권', '주가 급락']</t>
+          <t>['실적', '유상증자', 'RCPS']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1843,6 +1843,98 @@
         </is>
       </c>
       <c r="Z15" t="inlineStr">
+        <is>
+          <t>033790</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>한화시스템</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>72100</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>'-12.07%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E16" t="n">
+        <v>126</v>
+      </c>
+      <c r="F16" t="n">
+        <v>76</v>
+      </c>
+      <c r="G16" t="n">
+        <v>408</v>
+      </c>
+      <c r="H16" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>82000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>79400</v>
+      </c>
+      <c r="L16" t="n">
+        <v>79400</v>
+      </c>
+      <c r="M16" t="n">
+        <v>71100</v>
+      </c>
+      <c r="N16" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="O16" t="n">
+        <v>63886428350</v>
+      </c>
+      <c r="P16" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>44750</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-225000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-35000</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>공매도 비중 관련 논란 속에 주가 하락. 적정가 5만 원대 주장.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['공매도', '거래량', '적정가']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>272210</t>
         </is>

--- a/data/trending_integrated_20261020_10.xlsx
+++ b/data/trending_integrated_20261020_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76500</v>
+        <v>76600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.60%</t>
+          <t>'+18.76%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.29</v>
       </c>
       <c r="E2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G2" t="n">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="H2" t="n">
         <v>5.95</v>
@@ -601,7 +601,7 @@
         <v>68000</v>
       </c>
       <c r="L2" t="n">
-        <v>76700</v>
+        <v>77600</v>
       </c>
       <c r="M2" t="n">
         <v>66700</v>
@@ -610,7 +610,7 @@
         <v>5.66</v>
       </c>
       <c r="O2" t="n">
-        <v>76007258850</v>
+        <v>82318430900</v>
       </c>
       <c r="P2" t="n">
         <v>148300</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>반도체 관련주로서 지수 하락에도 불구하고 강한 상승세 기록. 2차전지 및 반도체 소부장 테마 기대감.</t>
+          <t>반도체 소부장 섹터 내에서 강세 보이며 지수 대비 높은 등락률 기록.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['반도체', '상승세', '테마 기대감']</t>
+          <t>['반도체', '소부장', '강세']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10670</v>
+        <v>10680</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.00%</t>
+          <t>'+17.11%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.86</v>
       </c>
       <c r="E3" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F3" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="H3" t="n">
         <v>0.88</v>
@@ -702,7 +702,7 @@
         <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>163268324590</v>
+        <v>167973167165</v>
       </c>
       <c r="P3" t="n">
         <v>11250</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇 사업 성장 기대감 및 7천억 원 수주 잔고 확보. 신고가 경신 및 1조 클럽 목표.</t>
+          <t>로봇 섹터 강세 속 신고가 기록 및 1조 클럽 기대감. 수주 잔고 7천억원.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇 사업', '수주 잔고', '신고가']</t>
+          <t>['로봇', '신고가', '수주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>녹십자엠에스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20100</v>
+        <v>3925</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.98%</t>
+          <t>'+4.67%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="H4" t="n">
-        <v>3.07</v>
+        <v>1.66</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19710</v>
+        <v>3750</v>
       </c>
       <c r="K4" t="n">
-        <v>19450</v>
+        <v>3770</v>
       </c>
       <c r="L4" t="n">
-        <v>21850</v>
+        <v>4285</v>
       </c>
       <c r="M4" t="n">
-        <v>19450</v>
+        <v>3755</v>
       </c>
       <c r="N4" t="n">
-        <v>3.32</v>
+        <v>1.66</v>
       </c>
       <c r="O4" t="n">
-        <v>79348097550</v>
+        <v>34948949269</v>
       </c>
       <c r="P4" t="n">
-        <v>22450</v>
+        <v>6660</v>
       </c>
       <c r="Q4" t="n">
-        <v>6320</v>
+        <v>2200</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-69000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇주 상승에 따른 보안주 동반 상승 기대감 속에서 변동성 확대 및 털기 가능성 언급.</t>
+          <t>차세대 피하주사 기술 관련 계약 체결 소식 있으나, 시장 전반의 하락세 영향으로 주가 부진.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇주', '보안주', '변동성']</t>
+          <t>['피하주사', '기술 계약', '시장 하락']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>142280</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42400</v>
+        <v>20050</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-1.28%</t>
+          <t>'+1.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.25</v>
       </c>
       <c r="E5" t="n">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="F5" t="n">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>705</v>
+        <v>105</v>
       </c>
       <c r="H5" t="n">
-        <v>13.11</v>
+        <v>3.07</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>42950</v>
+        <v>19710</v>
       </c>
       <c r="K5" t="n">
-        <v>42600</v>
+        <v>19450</v>
       </c>
       <c r="L5" t="n">
-        <v>43200</v>
+        <v>21850</v>
       </c>
       <c r="M5" t="n">
-        <v>41550</v>
+        <v>19450</v>
       </c>
       <c r="N5" t="n">
-        <v>13.04</v>
+        <v>3.32</v>
       </c>
       <c r="O5" t="n">
-        <v>8185377900</v>
+        <v>80529231700</v>
       </c>
       <c r="P5" t="n">
-        <v>69200</v>
+        <v>22450</v>
       </c>
       <c r="Q5" t="n">
-        <v>24150</v>
+        <v>6320</v>
       </c>
       <c r="R5" t="n">
-        <v>-11000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>C1 발표 및 담관암 FDA 승인 기대감 속에서 주가 횡보 및 추매 의견.</t>
+          <t>로봇 섹터와 연관 기대감 및 보안주로서의 역할 언급. 주가 변동성 및 개인 투자자 이탈에 대한 우려.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['C1 발표', 'FDA 승인', '추매']</t>
+          <t>['보안주', '로봇', '변동성']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>214500</v>
+        <v>42600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.61%</t>
+          <t>'-0.81%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>121</v>
       </c>
       <c r="F6" t="n">
-        <v>507</v>
+        <v>83</v>
       </c>
       <c r="G6" t="n">
-        <v>1142</v>
+        <v>735</v>
       </c>
       <c r="H6" t="n">
-        <v>46.04</v>
+        <v>13.11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>218000</v>
+        <v>42950</v>
       </c>
       <c r="K6" t="n">
-        <v>219500</v>
+        <v>42600</v>
       </c>
       <c r="L6" t="n">
-        <v>219500</v>
+        <v>43200</v>
       </c>
       <c r="M6" t="n">
-        <v>210000</v>
+        <v>41550</v>
       </c>
       <c r="N6" t="n">
-        <v>45.99</v>
+        <v>13.04</v>
       </c>
       <c r="O6" t="n">
-        <v>1149646197750</v>
+        <v>8663742325</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>69200</v>
       </c>
       <c r="Q6" t="n">
-        <v>94500</v>
+        <v>24150</v>
       </c>
       <c r="R6" t="n">
-        <v>400000</v>
+        <v>-11000</v>
       </c>
       <c r="S6" t="n">
-        <v>-408000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정부 정책에 대한 불만과 증시 부진에 대한 부정적인 게시글 다수.</t>
+          <t>C1 발표 및 담관암 FDA 승인 기대감 속에서 주가 횡보 및 추매 의견.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['정부 정책', '증시 부진', '불만']</t>
+          <t>['C1 발표', 'FDA 승인', '추매']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7310</v>
+        <v>214750</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.01%</t>
+          <t>'-1.49%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>32</v>
+        <v>508</v>
       </c>
       <c r="G7" t="n">
-        <v>150</v>
+        <v>1144</v>
       </c>
       <c r="H7" t="n">
-        <v>25.4</v>
+        <v>46.04</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7460</v>
+        <v>218000</v>
       </c>
       <c r="K7" t="n">
-        <v>7410</v>
+        <v>219500</v>
       </c>
       <c r="L7" t="n">
-        <v>7490</v>
+        <v>219500</v>
       </c>
       <c r="M7" t="n">
-        <v>7200</v>
+        <v>210000</v>
       </c>
       <c r="N7" t="n">
-        <v>25.42</v>
+        <v>45.99</v>
       </c>
       <c r="O7" t="n">
-        <v>6806015085</v>
+        <v>1216598449750</v>
       </c>
       <c r="P7" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>7190</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>-77000</v>
+        <v>400000</v>
       </c>
       <c r="S7" t="n">
-        <v>-15000</v>
+        <v>-408000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>실적 발표 후에도 주가 하락세 지속 및 외인 수급 부진에 대한 우려.</t>
+          <t>주가 부진에 대한 정치적 비판 및 정부 정책 관련 부정적 언급 다수.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['실적 부진', '외인 수급', '주가 하락']</t>
+          <t>['이재명', '정부 정책', '주가 관리']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17660</v>
+        <v>7300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-3.50%</t>
+          <t>'-2.14%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="H8" t="n">
-        <v>27.78</v>
+        <v>25.4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18300</v>
+        <v>7460</v>
       </c>
       <c r="K8" t="n">
-        <v>18140</v>
+        <v>7410</v>
       </c>
       <c r="L8" t="n">
-        <v>18140</v>
+        <v>7490</v>
       </c>
       <c r="M8" t="n">
-        <v>17280</v>
+        <v>7200</v>
       </c>
       <c r="N8" t="n">
-        <v>27.85</v>
+        <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>22608360195</v>
+        <v>7018785830</v>
       </c>
       <c r="P8" t="n">
-        <v>35350</v>
+        <v>17950</v>
       </c>
       <c r="Q8" t="n">
-        <v>17210</v>
+        <v>7190</v>
       </c>
       <c r="R8" t="n">
-        <v>-148000</v>
+        <v>-77000</v>
       </c>
       <c r="S8" t="n">
-        <v>-117000</v>
+        <v>-15000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>조선업 부진 및 반도체 관련 종목 동반 하락 우려 속에서 주가 하락세 지속.</t>
+          <t>3분기 영업이익 2,451억원 발표에도 불구하고 주가 하락 지속. FLiPP 등 기술 혁신 언급되나 투자자들은 부정적 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['조선업 부진', '반도체 하락', '주가 하락']</t>
+          <t>['영업이익', '주가 하락', '기술 혁신']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14410</v>
+        <v>14440</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.61%</t>
+          <t>'-3.41%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H9" t="n">
         <v>9.779999999999999</v>
@@ -1254,7 +1254,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>13135517120</v>
+        <v>13567002820</v>
       </c>
       <c r="P9" t="n">
         <v>40350</v>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1227000</v>
+        <v>17670</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.92%</t>
+          <t>'-3.44%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>597</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>1461</v>
+        <v>122</v>
       </c>
       <c r="H10" t="n">
-        <v>48.81</v>
+        <v>27.78</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1277000</v>
+        <v>18300</v>
       </c>
       <c r="K10" t="n">
-        <v>1265000</v>
+        <v>18140</v>
       </c>
       <c r="L10" t="n">
-        <v>1267000</v>
+        <v>18140</v>
       </c>
       <c r="M10" t="n">
-        <v>1183000</v>
+        <v>17280</v>
       </c>
       <c r="N10" t="n">
-        <v>48.82</v>
+        <v>27.85</v>
       </c>
       <c r="O10" t="n">
-        <v>1830056517000</v>
+        <v>23370265730</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>35350</v>
       </c>
       <c r="Q10" t="n">
-        <v>465500</v>
+        <v>17210</v>
       </c>
       <c r="R10" t="n">
-        <v>-136000</v>
+        <v>-148000</v>
       </c>
       <c r="S10" t="n">
-        <v>-76000</v>
+        <v>-117000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치권의 경제 정책 실패로 인한 주가 하락에 대한 강한 불만과 투자 철회 의견.</t>
+          <t>조선업 부진 및 반도체 관련 종목 동반 하락 우려 속에서 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['경제 정책 실패', '주가 하락', '정치권 비판']</t>
+          <t>['조선업 부진', '반도체 하락', '주가 하락']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2575</v>
+        <v>1230000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.45%</t>
+          <t>'-3.68%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.34</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>574</v>
       </c>
       <c r="G11" t="n">
-        <v>138</v>
+        <v>1496</v>
       </c>
       <c r="H11" t="n">
-        <v>1.14</v>
+        <v>48.81</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2695</v>
+        <v>1277000</v>
       </c>
       <c r="K11" t="n">
-        <v>2645</v>
+        <v>1265000</v>
       </c>
       <c r="L11" t="n">
-        <v>2715</v>
+        <v>1267000</v>
       </c>
       <c r="M11" t="n">
-        <v>2510</v>
+        <v>1183000</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8</v>
+        <v>48.82</v>
       </c>
       <c r="O11" t="n">
-        <v>24951381592</v>
+        <v>1945829650000</v>
       </c>
       <c r="P11" t="n">
-        <v>2755</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>865</v>
+        <v>465500</v>
       </c>
       <c r="R11" t="n">
-        <v>297000</v>
+        <v>-136000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-76000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1000억원 규모 하이브리드 부품 수주 공시 및 역대급 3분기 실적 기대감. 주가 상승 및 매수 기회 언급.</t>
+          <t>정치적 이슈 및 솔리다임 관련 부정적 전망과 함께 주가 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['하이브리드 부품', '수주', '실적']</t>
+          <t>['이재명', '솔리다임', '주가 하락']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,86 +1476,86 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31950</v>
+        <v>2560</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.89%</t>
+          <t>'-5.01%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.02</v>
+        <v>0.34</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="H12" t="n">
-        <v>12.79</v>
+        <v>1.14</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>33950</v>
+        <v>2695</v>
       </c>
       <c r="K12" t="n">
-        <v>33250</v>
+        <v>2645</v>
       </c>
       <c r="L12" t="n">
-        <v>34150</v>
+        <v>2715</v>
       </c>
       <c r="M12" t="n">
-        <v>31300</v>
+        <v>2510</v>
       </c>
       <c r="N12" t="n">
-        <v>12.81</v>
+        <v>0.8</v>
       </c>
       <c r="O12" t="n">
-        <v>35235122575</v>
+        <v>25273261772</v>
       </c>
       <c r="P12" t="n">
-        <v>59300</v>
+        <v>2755</v>
       </c>
       <c r="Q12" t="n">
-        <v>22000</v>
+        <v>865</v>
       </c>
       <c r="R12" t="n">
-        <v>-108000</v>
+        <v>297000</v>
       </c>
       <c r="S12" t="n">
-        <v>-12000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 태양광 관세 관련 승리 및 중간선거 결과에 따른 기대감. 매수 기회 언급.</t>
+          <t>미국 법인 하이브리드 부품 수주(1000억 규모) 및 역대급 3분기 실적 발표. 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['태양광', '미국 관세', '중간선거']</t>
+          <t>['하이브리드 부품', '수주', '실적']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1632</v>
+        <v>31950</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-6.64%</t>
+          <t>'-5.89%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>124</v>
+        <v>40</v>
       </c>
       <c r="F13" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="G13" t="n">
-        <v>234</v>
+        <v>116</v>
       </c>
       <c r="H13" t="n">
-        <v>1.77</v>
+        <v>12.79</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1748</v>
+        <v>33950</v>
       </c>
       <c r="K13" t="n">
-        <v>1706</v>
+        <v>33250</v>
       </c>
       <c r="L13" t="n">
-        <v>1895</v>
+        <v>34150</v>
       </c>
       <c r="M13" t="n">
-        <v>1625</v>
+        <v>31300</v>
       </c>
       <c r="N13" t="n">
-        <v>0.83</v>
+        <v>12.81</v>
       </c>
       <c r="O13" t="n">
-        <v>62417819987</v>
+        <v>36447992975</v>
       </c>
       <c r="P13" t="n">
-        <v>2970</v>
+        <v>59300</v>
       </c>
       <c r="Q13" t="n">
-        <v>890</v>
+        <v>22000</v>
       </c>
       <c r="R13" t="n">
-        <v>-149000</v>
+        <v>-108000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>스페이스X 계약 체결 관련 호재 공시로 인한 급등세 전망. 최근 3일간 코스피 수익률 3위 달성.</t>
+          <t>미국 태양광 관련 긍정적 뉴스 있으나, 전반적인 시장 하락 및 공매도 영향으로 주가 부진.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['스페이스X', '호재 공시', '급등']</t>
+          <t>['태양광', '공매도', '시장 하락']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8870</v>
+        <v>1622</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-8.74%</t>
+          <t>'-7.21%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>71</v>
+        <v>132</v>
       </c>
       <c r="F14" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="G14" t="n">
-        <v>153</v>
+        <v>242</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>1.77</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,47 +1699,47 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>9720</v>
+        <v>1748</v>
       </c>
       <c r="K14" t="n">
-        <v>9930</v>
+        <v>1706</v>
       </c>
       <c r="L14" t="n">
-        <v>9930</v>
+        <v>1895</v>
       </c>
       <c r="M14" t="n">
-        <v>8750</v>
+        <v>1603</v>
       </c>
       <c r="N14" t="n">
-        <v>6.15</v>
+        <v>0.83</v>
       </c>
       <c r="O14" t="n">
-        <v>11023052735</v>
+        <v>63556255663</v>
       </c>
       <c r="P14" t="n">
-        <v>14940</v>
+        <v>2970</v>
       </c>
       <c r="Q14" t="n">
-        <v>5390</v>
+        <v>890</v>
       </c>
       <c r="R14" t="n">
-        <v>-248000</v>
+        <v>-149000</v>
       </c>
       <c r="S14" t="n">
-        <v>-98000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>공매도 압력 속에서 변동성 확대 우려 및 단기 매매 관점의 게시글.</t>
+          <t>스페이스X 관련 호재 공시로 인한 급등세 기록. 3일간 코스피 수익률 3위 달성.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '변동성', '단기 매매']</t>
+          <t>['스페이스X', '호재', '급등']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,77 +1752,77 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8030</v>
+        <v>8830</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-10.18%</t>
+          <t>'-9.16%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.38</v>
+        <v>-0.15</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="F15" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="H15" t="n">
-        <v>36.01</v>
+        <v>6</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8940</v>
+        <v>9720</v>
       </c>
       <c r="K15" t="n">
-        <v>9000</v>
+        <v>9930</v>
       </c>
       <c r="L15" t="n">
-        <v>9010</v>
+        <v>9930</v>
       </c>
       <c r="M15" t="n">
-        <v>7750</v>
+        <v>8750</v>
       </c>
       <c r="N15" t="n">
-        <v>36.39</v>
+        <v>6.15</v>
       </c>
       <c r="O15" t="n">
-        <v>14270476815</v>
+        <v>11460943720</v>
       </c>
       <c r="P15" t="n">
-        <v>19150</v>
+        <v>14940</v>
       </c>
       <c r="Q15" t="n">
-        <v>3570</v>
+        <v>5390</v>
       </c>
       <c r="R15" t="n">
-        <v>-110000</v>
+        <v>-248000</v>
       </c>
       <c r="S15" t="n">
-        <v>-5000</v>
+        <v>-98000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
+          <t>테슬라 관련 기대감 있으나, 주가 하락 및 고평가 부담에 대한 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['실적', '유상증자', 'RCPS']</t>
+          <t>['테슬라', '주가 하락', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,86 +1844,86 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>72100</v>
+        <v>8040</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-12.07%</t>
+          <t>'-10.07%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.06</v>
+        <v>-0.38</v>
       </c>
       <c r="E16" t="n">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="F16" t="n">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G16" t="n">
-        <v>408</v>
+        <v>83</v>
       </c>
       <c r="H16" t="n">
-        <v>9.380000000000001</v>
+        <v>36.01</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>82000</v>
+        <v>8940</v>
       </c>
       <c r="K16" t="n">
-        <v>79400</v>
+        <v>9000</v>
       </c>
       <c r="L16" t="n">
-        <v>79400</v>
+        <v>9010</v>
       </c>
       <c r="M16" t="n">
-        <v>71100</v>
+        <v>7750</v>
       </c>
       <c r="N16" t="n">
-        <v>9.44</v>
+        <v>36.39</v>
       </c>
       <c r="O16" t="n">
-        <v>63886428350</v>
+        <v>14442200650</v>
       </c>
       <c r="P16" t="n">
-        <v>184000</v>
+        <v>19150</v>
       </c>
       <c r="Q16" t="n">
-        <v>44750</v>
+        <v>3570</v>
       </c>
       <c r="R16" t="n">
-        <v>-225000</v>
+        <v>-110000</v>
       </c>
       <c r="S16" t="n">
-        <v>-35000</v>
+        <v>-5000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>공매도 비중 관련 논란 속에 주가 하락. 적정가 5만 원대 주장.</t>
+          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공매도', '거래량', '적정가']</t>
+          <t>['실적', '유상증자', 'RCPS']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1935,6 +1935,98 @@
         </is>
       </c>
       <c r="Z16" t="inlineStr">
+        <is>
+          <t>033790</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>한화시스템</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>71500</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>'-12.80%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E17" t="n">
+        <v>132</v>
+      </c>
+      <c r="F17" t="n">
+        <v>79</v>
+      </c>
+      <c r="G17" t="n">
+        <v>437</v>
+      </c>
+      <c r="H17" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>82000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>79400</v>
+      </c>
+      <c r="L17" t="n">
+        <v>79400</v>
+      </c>
+      <c r="M17" t="n">
+        <v>71100</v>
+      </c>
+      <c r="N17" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="O17" t="n">
+        <v>67291572550</v>
+      </c>
+      <c r="P17" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>44750</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-225000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-35000</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>공매도 비중 관련 논란 속에 주가 하락. 적정가 5만 원대 주장.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>['공매도', '거래량', '적정가']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
         <is>
           <t>272210</t>
         </is>
